--- a/real_estate_manual_with_lat_long.xlsx
+++ b/real_estate_manual_with_lat_long.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nay/Library/Mobile Documents/com~apple~CloudDocs/Uni/SIT720/Task 8.2D/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2FB0C8-08DE-CE44-9187-CFB862E5A62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4368D1BC-282C-2C42-AD32-9360F621CCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="50480" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="315">
   <si>
     <t>sold_price</t>
   </si>
@@ -535,6 +535,12 @@
     <t>(-37.7957667, 144.8941088)</t>
   </si>
   <si>
+    <t>388 Barkly Street</t>
+  </si>
+  <si>
+    <t>(-37.8807947, 144.9787938)</t>
+  </si>
+  <si>
     <t>5 Summerhill Road</t>
   </si>
   <si>
@@ -853,6 +859,12 @@
     <t>(-38.3387881, 144.9642515)</t>
   </si>
   <si>
+    <t>84 Westgarth Street</t>
+  </si>
+  <si>
+    <t>(-37.7818407, 145.0012404)</t>
+  </si>
+  <si>
     <t>37 Jenkins Street</t>
   </si>
   <si>
@@ -952,13 +964,7 @@
     <t>(-37.7689107, 144.9942279)</t>
   </si>
   <si>
-    <t>19 Odessa Steet</t>
-  </si>
-  <si>
-    <t>388 Barkly Street</t>
-  </si>
-  <si>
-    <t>84 Westgarth Street</t>
+    <t>19 Odessa Street</t>
   </si>
 </sst>
 </file>
@@ -1328,10 +1334,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="4" max="4" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -1869,7 +1871,7 @@
         <v>3182</v>
       </c>
       <c r="D16" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E16" t="s">
         <v>13</v>
@@ -4141,7 +4143,7 @@
         <v>3011</v>
       </c>
       <c r="D81" t="s">
-        <v>311</v>
+        <v>171</v>
       </c>
       <c r="E81" t="s">
         <v>13</v>
@@ -4160,6 +4162,9 @@
       </c>
       <c r="J81" s="2">
         <v>45602</v>
+      </c>
+      <c r="K81" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
@@ -4173,7 +4178,7 @@
         <v>3011</v>
       </c>
       <c r="D82" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E82" t="s">
         <v>13</v>
@@ -4194,7 +4199,7 @@
         <v>45934</v>
       </c>
       <c r="K82" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
@@ -4208,7 +4213,7 @@
         <v>3011</v>
       </c>
       <c r="D83" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E83" t="s">
         <v>13</v>
@@ -4229,7 +4234,7 @@
         <v>45924</v>
       </c>
       <c r="K83" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
@@ -4243,7 +4248,7 @@
         <v>3011</v>
       </c>
       <c r="D84" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E84" t="s">
         <v>13</v>
@@ -4264,7 +4269,7 @@
         <v>45906</v>
       </c>
       <c r="K84" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
@@ -4278,7 +4283,7 @@
         <v>3011</v>
       </c>
       <c r="D85" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E85" t="s">
         <v>13</v>
@@ -4299,7 +4304,7 @@
         <v>45894</v>
       </c>
       <c r="K85" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
@@ -4313,7 +4318,7 @@
         <v>3011</v>
       </c>
       <c r="D86" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E86" t="s">
         <v>13</v>
@@ -4334,7 +4339,7 @@
         <v>45885</v>
       </c>
       <c r="K86" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
@@ -4348,7 +4353,7 @@
         <v>3011</v>
       </c>
       <c r="D87" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E87" t="s">
         <v>13</v>
@@ -4369,7 +4374,7 @@
         <v>45871</v>
       </c>
       <c r="K87" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
@@ -4383,7 +4388,7 @@
         <v>3011</v>
       </c>
       <c r="D88" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E88" t="s">
         <v>13</v>
@@ -4404,7 +4409,7 @@
         <v>45869</v>
       </c>
       <c r="K88" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
@@ -4418,7 +4423,7 @@
         <v>3011</v>
       </c>
       <c r="D89" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E89" t="s">
         <v>13</v>
@@ -4439,7 +4444,7 @@
         <v>45857</v>
       </c>
       <c r="K89" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
@@ -4453,7 +4458,7 @@
         <v>3011</v>
       </c>
       <c r="D90" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E90" t="s">
         <v>13</v>
@@ -4474,7 +4479,7 @@
         <v>45852</v>
       </c>
       <c r="K90" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
@@ -4488,7 +4493,7 @@
         <v>3011</v>
       </c>
       <c r="D91" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E91" t="s">
         <v>13</v>
@@ -4509,7 +4514,7 @@
         <v>45850</v>
       </c>
       <c r="K91" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
@@ -4523,7 +4528,7 @@
         <v>3011</v>
       </c>
       <c r="D92" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E92" t="s">
         <v>13</v>
@@ -4544,7 +4549,7 @@
         <v>45849</v>
       </c>
       <c r="K92" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
@@ -4558,7 +4563,7 @@
         <v>3011</v>
       </c>
       <c r="D93" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E93" t="s">
         <v>13</v>
@@ -4579,7 +4584,7 @@
         <v>45847</v>
       </c>
       <c r="K93" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
@@ -4593,7 +4598,7 @@
         <v>3011</v>
       </c>
       <c r="D94" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E94" t="s">
         <v>13</v>
@@ -4614,7 +4619,7 @@
         <v>45843</v>
       </c>
       <c r="K94" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
@@ -4628,7 +4633,7 @@
         <v>3011</v>
       </c>
       <c r="D95" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E95" t="s">
         <v>13</v>
@@ -4649,7 +4654,7 @@
         <v>45834</v>
       </c>
       <c r="K95" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
@@ -4663,7 +4668,7 @@
         <v>3011</v>
       </c>
       <c r="D96" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E96" t="s">
         <v>13</v>
@@ -4684,7 +4689,7 @@
         <v>45818</v>
       </c>
       <c r="K96" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
@@ -4698,7 +4703,7 @@
         <v>3011</v>
       </c>
       <c r="D97" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E97" t="s">
         <v>13</v>
@@ -4719,7 +4724,7 @@
         <v>45813</v>
       </c>
       <c r="K97" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
@@ -4733,7 +4738,7 @@
         <v>3011</v>
       </c>
       <c r="D98" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E98" t="s">
         <v>13</v>
@@ -4754,7 +4759,7 @@
         <v>45801</v>
       </c>
       <c r="K98" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
@@ -4768,7 +4773,7 @@
         <v>3011</v>
       </c>
       <c r="D99" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E99" t="s">
         <v>13</v>
@@ -4789,7 +4794,7 @@
         <v>45785</v>
       </c>
       <c r="K99" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
@@ -4803,7 +4808,7 @@
         <v>3011</v>
       </c>
       <c r="D100" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E100" t="s">
         <v>13</v>
@@ -4824,7 +4829,7 @@
         <v>45748</v>
       </c>
       <c r="K100" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
@@ -4838,7 +4843,7 @@
         <v>3011</v>
       </c>
       <c r="D101" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E101" t="s">
         <v>13</v>
@@ -4859,7 +4864,7 @@
         <v>45739</v>
       </c>
       <c r="K101" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
@@ -4867,13 +4872,13 @@
         <v>1725000</v>
       </c>
       <c r="B102" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C102">
         <v>3070</v>
       </c>
       <c r="D102" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E102" t="s">
         <v>13</v>
@@ -4894,7 +4899,7 @@
         <v>46153</v>
       </c>
       <c r="K102" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
@@ -4902,16 +4907,16 @@
         <v>1287000</v>
       </c>
       <c r="B103" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C103">
         <v>3070</v>
       </c>
       <c r="D103" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E103" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F103">
         <v>2</v>
@@ -4929,7 +4934,7 @@
         <v>46130</v>
       </c>
       <c r="K103" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
@@ -4937,13 +4942,13 @@
         <v>3140000</v>
       </c>
       <c r="B104" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C104">
         <v>3070</v>
       </c>
       <c r="D104" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E104" t="s">
         <v>13</v>
@@ -4964,7 +4969,7 @@
         <v>46127</v>
       </c>
       <c r="K104" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
@@ -4972,13 +4977,13 @@
         <v>1500000</v>
       </c>
       <c r="B105" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C105">
         <v>3070</v>
       </c>
       <c r="D105" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E105" t="s">
         <v>13</v>
@@ -4999,7 +5004,7 @@
         <v>46114</v>
       </c>
       <c r="K105" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
@@ -5007,13 +5012,13 @@
         <v>1825000</v>
       </c>
       <c r="B106" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C106">
         <v>3070</v>
       </c>
       <c r="D106" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E106" t="s">
         <v>13</v>
@@ -5034,7 +5039,7 @@
         <v>46109</v>
       </c>
       <c r="K106" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
@@ -5042,13 +5047,13 @@
         <v>1875000</v>
       </c>
       <c r="B107" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C107">
         <v>3070</v>
       </c>
       <c r="D107" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E107" t="s">
         <v>13</v>
@@ -5069,7 +5074,7 @@
         <v>46081</v>
       </c>
       <c r="K107" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
@@ -5077,13 +5082,13 @@
         <v>1800000</v>
       </c>
       <c r="B108" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C108">
         <v>3070</v>
       </c>
       <c r="D108" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E108" t="s">
         <v>13</v>
@@ -5104,7 +5109,7 @@
         <v>46081</v>
       </c>
       <c r="K108" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
@@ -5112,13 +5117,13 @@
         <v>1650000</v>
       </c>
       <c r="B109" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C109">
         <v>3070</v>
       </c>
       <c r="D109" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E109" t="s">
         <v>13</v>
@@ -5139,7 +5144,7 @@
         <v>46081</v>
       </c>
       <c r="K109" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
@@ -5147,13 +5152,13 @@
         <v>2335000</v>
       </c>
       <c r="B110" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C110">
         <v>3070</v>
       </c>
       <c r="D110" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E110" t="s">
         <v>13</v>
@@ -5174,7 +5179,7 @@
         <v>46074</v>
       </c>
       <c r="K110" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
@@ -5182,13 +5187,13 @@
         <v>1330000</v>
       </c>
       <c r="B111" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C111">
         <v>3070</v>
       </c>
       <c r="D111" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E111" t="s">
         <v>13</v>
@@ -5209,7 +5214,7 @@
         <v>46031</v>
       </c>
       <c r="K111" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
@@ -5217,13 +5222,13 @@
         <v>2150000</v>
       </c>
       <c r="B112" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C112">
         <v>3070</v>
       </c>
       <c r="D112" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E112" t="s">
         <v>13</v>
@@ -5244,7 +5249,7 @@
         <v>46028</v>
       </c>
       <c r="K112" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
@@ -5252,13 +5257,13 @@
         <v>1335000</v>
       </c>
       <c r="B113" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C113">
         <v>3070</v>
       </c>
       <c r="D113" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E113" t="s">
         <v>13</v>
@@ -5279,7 +5284,7 @@
         <v>46028</v>
       </c>
       <c r="K113" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
@@ -5287,13 +5292,13 @@
         <v>1300000</v>
       </c>
       <c r="B114" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C114">
         <v>3070</v>
       </c>
       <c r="D114" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E114" t="s">
         <v>13</v>
@@ -5314,7 +5319,7 @@
         <v>46025</v>
       </c>
       <c r="K114" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
@@ -5322,13 +5327,13 @@
         <v>2100000</v>
       </c>
       <c r="B115" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C115">
         <v>3070</v>
       </c>
       <c r="D115" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E115" t="s">
         <v>13</v>
@@ -5349,7 +5354,7 @@
         <v>46011</v>
       </c>
       <c r="K115" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
@@ -5357,13 +5362,13 @@
         <v>1368500</v>
       </c>
       <c r="B116" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C116">
         <v>3070</v>
       </c>
       <c r="D116" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E116" t="s">
         <v>13</v>
@@ -5384,7 +5389,7 @@
         <v>46011</v>
       </c>
       <c r="K116" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
@@ -5392,13 +5397,13 @@
         <v>2375000</v>
       </c>
       <c r="B117" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C117">
         <v>3070</v>
       </c>
       <c r="D117" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E117" t="s">
         <v>13</v>
@@ -5419,7 +5424,7 @@
         <v>46009</v>
       </c>
       <c r="K117" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
@@ -5427,13 +5432,13 @@
         <v>1230000</v>
       </c>
       <c r="B118" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C118">
         <v>3070</v>
       </c>
       <c r="D118" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E118" t="s">
         <v>13</v>
@@ -5454,7 +5459,7 @@
         <v>46008</v>
       </c>
       <c r="K118" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
@@ -5462,13 +5467,13 @@
         <v>2335000</v>
       </c>
       <c r="B119" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C119">
         <v>3070</v>
       </c>
       <c r="D119" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E119" t="s">
         <v>13</v>
@@ -5489,7 +5494,7 @@
         <v>46004</v>
       </c>
       <c r="K119" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
@@ -5497,13 +5502,13 @@
         <v>2300000</v>
       </c>
       <c r="B120" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C120">
         <v>3070</v>
       </c>
       <c r="D120" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E120" t="s">
         <v>13</v>
@@ -5524,7 +5529,7 @@
         <v>46004</v>
       </c>
       <c r="K120" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
@@ -5532,13 +5537,13 @@
         <v>1715000</v>
       </c>
       <c r="B121" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C121">
         <v>3070</v>
       </c>
       <c r="D121" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E121" t="s">
         <v>13</v>
@@ -5559,7 +5564,7 @@
         <v>46004</v>
       </c>
       <c r="K121" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
@@ -5567,13 +5572,13 @@
         <v>1295000</v>
       </c>
       <c r="B122" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C122">
         <v>3070</v>
       </c>
       <c r="D122" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E122" t="s">
         <v>13</v>
@@ -5594,7 +5599,7 @@
         <v>46004</v>
       </c>
       <c r="K122" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
@@ -5602,13 +5607,13 @@
         <v>930000</v>
       </c>
       <c r="B123" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C123">
         <v>3070</v>
       </c>
       <c r="D123" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E123" t="s">
         <v>13</v>
@@ -5629,7 +5634,7 @@
         <v>46004</v>
       </c>
       <c r="K123" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
@@ -5637,13 +5642,13 @@
         <v>1080000</v>
       </c>
       <c r="B124" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C124">
         <v>3070</v>
       </c>
       <c r="D124" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E124" t="s">
         <v>13</v>
@@ -5664,7 +5669,7 @@
         <v>46003</v>
       </c>
       <c r="K124" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
@@ -5672,13 +5677,13 @@
         <v>3020000</v>
       </c>
       <c r="B125" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C125">
         <v>3070</v>
       </c>
       <c r="D125" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E125" t="s">
         <v>13</v>
@@ -5699,7 +5704,7 @@
         <v>46001</v>
       </c>
       <c r="K125" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
@@ -5707,13 +5712,13 @@
         <v>3670000</v>
       </c>
       <c r="B126" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C126">
         <v>3070</v>
       </c>
       <c r="D126" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E126" t="s">
         <v>13</v>
@@ -5734,7 +5739,7 @@
         <v>45997</v>
       </c>
       <c r="K126" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
@@ -5742,13 +5747,13 @@
         <v>1570000</v>
       </c>
       <c r="B127" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C127">
         <v>3070</v>
       </c>
       <c r="D127" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E127" t="s">
         <v>13</v>
@@ -5769,7 +5774,7 @@
         <v>45997</v>
       </c>
       <c r="K127" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
@@ -5777,13 +5782,13 @@
         <v>2000000</v>
       </c>
       <c r="B128" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C128">
         <v>3070</v>
       </c>
       <c r="D128" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E128" t="s">
         <v>13</v>
@@ -5804,7 +5809,7 @@
         <v>45994</v>
       </c>
       <c r="K128" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
@@ -5812,13 +5817,13 @@
         <v>2430000</v>
       </c>
       <c r="B129" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C129">
         <v>3070</v>
       </c>
       <c r="D129" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E129" t="s">
         <v>13</v>
@@ -5839,7 +5844,7 @@
         <v>45990</v>
       </c>
       <c r="K129" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
@@ -5847,13 +5852,13 @@
         <v>1960000</v>
       </c>
       <c r="B130" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C130">
         <v>3070</v>
       </c>
       <c r="D130" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E130" t="s">
         <v>13</v>
@@ -5874,7 +5879,7 @@
         <v>45990</v>
       </c>
       <c r="K130" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.2">
@@ -5882,13 +5887,13 @@
         <v>2810000</v>
       </c>
       <c r="B131" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C131">
         <v>3070</v>
       </c>
       <c r="D131" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E131" t="s">
         <v>13</v>
@@ -5909,7 +5914,7 @@
         <v>45989</v>
       </c>
       <c r="K131" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
@@ -5917,13 +5922,13 @@
         <v>1815000</v>
       </c>
       <c r="B132" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C132">
         <v>3070</v>
       </c>
       <c r="D132" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E132" t="s">
         <v>13</v>
@@ -5944,7 +5949,7 @@
         <v>45981</v>
       </c>
       <c r="K132" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.2">
@@ -5952,13 +5957,13 @@
         <v>3272000</v>
       </c>
       <c r="B133" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C133">
         <v>3070</v>
       </c>
       <c r="D133" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E133" t="s">
         <v>13</v>
@@ -5979,7 +5984,7 @@
         <v>45976</v>
       </c>
       <c r="K133" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
@@ -5987,13 +5992,13 @@
         <v>2250000</v>
       </c>
       <c r="B134" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C134">
         <v>3070</v>
       </c>
       <c r="D134" t="s">
-        <v>312</v>
+        <v>279</v>
       </c>
       <c r="E134" t="s">
         <v>13</v>
@@ -6012,6 +6017,9 @@
       </c>
       <c r="J134" s="2">
         <v>45619</v>
+      </c>
+      <c r="K134" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.2">
@@ -6019,13 +6027,13 @@
         <v>1830000</v>
       </c>
       <c r="B135" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C135">
         <v>3070</v>
       </c>
       <c r="D135" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E135" t="s">
         <v>13</v>
@@ -6046,7 +6054,7 @@
         <v>45975</v>
       </c>
       <c r="K135" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
@@ -6054,13 +6062,13 @@
         <v>1690000</v>
       </c>
       <c r="B136" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C136">
         <v>3070</v>
       </c>
       <c r="D136" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E136" t="s">
         <v>13</v>
@@ -6081,7 +6089,7 @@
         <v>45974</v>
       </c>
       <c r="K136" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
@@ -6089,13 +6097,13 @@
         <v>1600000</v>
       </c>
       <c r="B137" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C137">
         <v>3070</v>
       </c>
       <c r="D137" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E137" t="s">
         <v>13</v>
@@ -6116,7 +6124,7 @@
         <v>45960</v>
       </c>
       <c r="K137" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
@@ -6124,13 +6132,13 @@
         <v>2390000</v>
       </c>
       <c r="B138" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C138">
         <v>3070</v>
       </c>
       <c r="D138" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E138" t="s">
         <v>13</v>
@@ -6151,7 +6159,7 @@
         <v>45955</v>
       </c>
       <c r="K138" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
@@ -6159,13 +6167,13 @@
         <v>2200000</v>
       </c>
       <c r="B139" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C139">
         <v>3070</v>
       </c>
       <c r="D139" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E139" t="s">
         <v>13</v>
@@ -6186,7 +6194,7 @@
         <v>45955</v>
       </c>
       <c r="K139" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
@@ -6194,13 +6202,13 @@
         <v>1201195</v>
       </c>
       <c r="B140" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C140">
         <v>3070</v>
       </c>
       <c r="D140" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E140" t="s">
         <v>13</v>
@@ -6221,7 +6229,7 @@
         <v>45952</v>
       </c>
       <c r="K140" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
@@ -6229,13 +6237,13 @@
         <v>2100000</v>
       </c>
       <c r="B141" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C141">
         <v>3070</v>
       </c>
       <c r="D141" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E141" t="s">
         <v>13</v>
@@ -6256,7 +6264,7 @@
         <v>45944</v>
       </c>
       <c r="K141" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
@@ -6264,13 +6272,13 @@
         <v>2920000</v>
       </c>
       <c r="B142" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C142">
         <v>3070</v>
       </c>
       <c r="D142" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E142" t="s">
         <v>13</v>
@@ -6291,7 +6299,7 @@
         <v>45941</v>
       </c>
       <c r="K142" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.2">
@@ -6299,13 +6307,13 @@
         <v>2310000</v>
       </c>
       <c r="B143" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C143">
         <v>3070</v>
       </c>
       <c r="D143" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E143" t="s">
         <v>13</v>
@@ -6326,7 +6334,7 @@
         <v>45937</v>
       </c>
       <c r="K143" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
@@ -6334,13 +6342,13 @@
         <v>3029000</v>
       </c>
       <c r="B144" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C144">
         <v>3070</v>
       </c>
       <c r="D144" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E144" t="s">
         <v>13</v>
@@ -6361,7 +6369,7 @@
         <v>45920</v>
       </c>
       <c r="K144" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.2">
@@ -6369,13 +6377,13 @@
         <v>2375000</v>
       </c>
       <c r="B145" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C145">
         <v>3070</v>
       </c>
       <c r="D145" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E145" t="s">
         <v>13</v>
@@ -6396,7 +6404,7 @@
         <v>45920</v>
       </c>
       <c r="K145" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.2">
@@ -6404,13 +6412,13 @@
         <v>1315000</v>
       </c>
       <c r="B146" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C146">
         <v>3070</v>
       </c>
       <c r="D146" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E146" t="s">
         <v>13</v>
@@ -6431,7 +6439,7 @@
         <v>45916</v>
       </c>
       <c r="K146" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.2">
@@ -6439,13 +6447,13 @@
         <v>3613622</v>
       </c>
       <c r="B147" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C147">
         <v>3070</v>
       </c>
       <c r="D147" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E147" t="s">
         <v>13</v>
@@ -6466,7 +6474,7 @@
         <v>45915</v>
       </c>
       <c r="K147" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.2">
@@ -6474,13 +6482,13 @@
         <v>1447500</v>
       </c>
       <c r="B148" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C148">
         <v>3070</v>
       </c>
       <c r="D148" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E148" t="s">
         <v>13</v>
@@ -6501,7 +6509,7 @@
         <v>45913</v>
       </c>
       <c r="K148" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.2">
@@ -6509,13 +6517,13 @@
         <v>1348000</v>
       </c>
       <c r="B149" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C149">
         <v>3070</v>
       </c>
       <c r="D149" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E149" t="s">
         <v>13</v>
@@ -6536,7 +6544,7 @@
         <v>45913</v>
       </c>
       <c r="K149" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.2">
@@ -6544,13 +6552,13 @@
         <v>2840000</v>
       </c>
       <c r="B150" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C150">
         <v>3070</v>
       </c>
       <c r="D150" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E150" t="s">
         <v>13</v>
@@ -6571,7 +6579,7 @@
         <v>45906</v>
       </c>
       <c r="K150" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.2">
@@ -6579,13 +6587,13 @@
         <v>1550000</v>
       </c>
       <c r="B151" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C151">
         <v>3070</v>
       </c>
       <c r="D151" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E151" t="s">
         <v>13</v>
@@ -6606,7 +6614,7 @@
         <v>45904</v>
       </c>
       <c r="K151" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/real_estate_manual_with_lat_long.xlsx
+++ b/real_estate_manual_with_lat_long.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nay/Library/Mobile Documents/com~apple~CloudDocs/Uni/SIT720/Task 8.2D/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4368D1BC-282C-2C42-AD32-9360F621CCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8BEDA3-A6C8-7B46-89FA-5BAA33EB1CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="50480" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -972,7 +972,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -1029,7 +1029,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1334,6 +1334,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="19.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
